--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.5072018159867</v>
+        <v>9.18242029509784</v>
       </c>
       <c r="D2" t="n">
-        <v>55.82133925859598</v>
+        <v>9.070967629521846</v>
       </c>
       <c r="E2" t="n">
-        <v>14.79299147432041</v>
+        <v>2.403861114577067</v>
       </c>
       <c r="F2" t="n">
-        <v>11.91534418153102</v>
+        <v>1.93624342949879</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.92121886734589</v>
+        <v>4.374698065943707</v>
       </c>
       <c r="D3" t="n">
-        <v>31.99065089553394</v>
+        <v>5.198480770524266</v>
       </c>
       <c r="E3" t="n">
-        <v>14.79299147432041</v>
+        <v>2.403861114577067</v>
       </c>
       <c r="F3" t="n">
-        <v>11.91534418153102</v>
+        <v>1.93624342949879</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
